--- a/src/test/res/disegno-pruebas-secuencias-collatz.xlsx
+++ b/src/test/res/disegno-pruebas-secuencias-collatz.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11115" windowHeight="7935" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11115" windowHeight="7935"/>
   </bookViews>
   <sheets>
     <sheet name="Diseño pruebas siguienteCollatz" sheetId="2" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="38">
   <si>
     <t>Parámetro</t>
   </si>
@@ -40,12 +40,6 @@
     <t>n</t>
   </si>
   <si>
-    <t>n &gt; 0 y par</t>
-  </si>
-  <si>
-    <t>n &gt; 0 e impar</t>
-  </si>
-  <si>
     <t>n &lt;= 0</t>
   </si>
   <si>
@@ -65,9 +59,6 @@
   </si>
   <si>
     <t>Casos de prueba (clases no válidas)</t>
-  </si>
-  <si>
-    <t>IllegalArgumentException</t>
   </si>
   <si>
     <t>this.inicio</t>
@@ -149,6 +140,21 @@
       </rPr>
       <t>test basis</t>
     </r>
+  </si>
+  <si>
+    <t>n par</t>
+  </si>
+  <si>
+    <t>n impar</t>
+  </si>
+  <si>
+    <t>1, 2</t>
+  </si>
+  <si>
+    <t>1, 3</t>
+  </si>
+  <si>
+    <t>Lo obviamos (la comprobación se hace en el constructor)</t>
   </si>
 </sst>
 </file>
@@ -235,7 +241,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="40">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -750,6 +756,41 @@
         <color indexed="64"/>
       </top>
       <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
       </bottom>
       <diagonal/>
@@ -762,7 +803,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -831,9 +872,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1" applyAlignment="1">
@@ -959,6 +997,15 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="38" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1443,68 +1490,68 @@
   <sheetData>
     <row r="2" spans="2:12" ht="23.25" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="65" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="I5" s="65" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
+      <c r="B5" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="I5" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
     </row>
     <row r="6" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="66" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="68"/>
+      <c r="C7" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="66"/>
+      <c r="E7" s="65" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="67"/>
       <c r="I7" s="16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J7" s="17" t="s">
         <v>3</v>
       </c>
       <c r="K7" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L7" s="18" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="69" t="s">
+      <c r="B8" s="68" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="2">
         <v>1</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="E8" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="I8" s="19" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="J8" s="20">
         <v>40</v>
@@ -1512,22 +1559,22 @@
       <c r="K8" s="20">
         <v>20</v>
       </c>
-      <c r="L8" s="21">
-        <v>1</v>
+      <c r="L8" s="21" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="70"/>
-      <c r="C9" s="6">
-        <v>2</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="8"/>
+      <c r="B9" s="74"/>
+      <c r="C9" s="75">
+        <v>2</v>
+      </c>
+      <c r="D9" s="76" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="75"/>
+      <c r="F9" s="77"/>
       <c r="I9" s="22" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="J9" s="23">
         <v>13</v>
@@ -1535,16 +1582,20 @@
       <c r="K9" s="23">
         <v>40</v>
       </c>
-      <c r="L9" s="24">
-        <v>2</v>
+      <c r="L9" s="24" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="10"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="11"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="11"/>
+      <c r="B10" s="69"/>
+      <c r="C10" s="6">
+        <v>3</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="E10" s="7"/>
+      <c r="F10" s="8"/>
       <c r="I10" s="25"/>
       <c r="J10" s="25"/>
       <c r="K10" s="25"/>
@@ -1552,7 +1603,7 @@
     </row>
     <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="I11" s="26" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J11" s="27">
         <v>20</v>
@@ -1560,13 +1611,13 @@
       <c r="K11" s="27">
         <v>10</v>
       </c>
-      <c r="L11" s="28">
-        <v>1</v>
+      <c r="L11" s="28" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="I12" s="19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J12" s="20">
         <f>K11</f>
@@ -1575,13 +1626,13 @@
       <c r="K12" s="20">
         <v>5</v>
       </c>
-      <c r="L12" s="29">
-        <v>1</v>
+      <c r="L12" s="29" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="I13" s="19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J13" s="20">
         <f t="shared" ref="J13:J17" si="0">K12</f>
@@ -1590,13 +1641,13 @@
       <c r="K13" s="20">
         <v>16</v>
       </c>
-      <c r="L13" s="29">
-        <v>2</v>
+      <c r="L13" s="29" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="I14" s="19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J14" s="20">
         <f t="shared" si="0"/>
@@ -1605,13 +1656,13 @@
       <c r="K14" s="20">
         <v>8</v>
       </c>
-      <c r="L14" s="29">
-        <v>1</v>
+      <c r="L14" s="29" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="I15" s="19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J15" s="20">
         <f t="shared" si="0"/>
@@ -1620,13 +1671,13 @@
       <c r="K15" s="20">
         <v>4</v>
       </c>
-      <c r="L15" s="29">
-        <v>1</v>
+      <c r="L15" s="29" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="I16" s="19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J16" s="20">
         <f t="shared" si="0"/>
@@ -1635,13 +1686,13 @@
       <c r="K16" s="20">
         <v>2</v>
       </c>
-      <c r="L16" s="29">
-        <v>1</v>
+      <c r="L16" s="29" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="9:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I17" s="22" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J17" s="23">
         <f t="shared" si="0"/>
@@ -1650,45 +1701,45 @@
       <c r="K17" s="23">
         <v>1</v>
       </c>
-      <c r="L17" s="30">
-        <v>1</v>
+      <c r="L17" s="30" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="20" spans="9:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="I20" s="65" t="s">
-        <v>12</v>
-      </c>
-      <c r="J20" s="65"/>
-      <c r="K20" s="65"/>
-      <c r="L20" s="65"/>
+      <c r="I20" s="64" t="s">
+        <v>10</v>
+      </c>
+      <c r="J20" s="64"/>
+      <c r="K20" s="64"/>
+      <c r="L20" s="64"/>
     </row>
     <row r="21" spans="9:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="9:12" x14ac:dyDescent="0.25">
       <c r="I22" s="16" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J22" s="17" t="s">
         <v>3</v>
       </c>
       <c r="K22" s="17" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L22" s="18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23" spans="9:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="9:12" ht="45.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="I23" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="J23" s="32">
+        <v>27</v>
+      </c>
+      <c r="J23" s="31">
         <v>0</v>
       </c>
-      <c r="K23" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="L23" s="33">
-        <v>3</v>
+      <c r="K23" s="78" t="s">
+        <v>37</v>
+      </c>
+      <c r="L23" s="32">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1697,8 +1748,8 @@
     <mergeCell ref="I20:L20"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="E7:F7"/>
-    <mergeCell ref="B8:B9"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B8:B10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -1725,68 +1776,68 @@
   <sheetData>
     <row r="2" spans="2:11" ht="23.25" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="5" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="65" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="H5" s="65" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
+      <c r="B5" s="64" t="s">
+        <v>5</v>
+      </c>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="H5" s="64" t="s">
+        <v>9</v>
+      </c>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
     </row>
     <row r="6" spans="2:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="66" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="67"/>
-      <c r="E7" s="66" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="68"/>
-      <c r="H7" s="34" t="s">
+      <c r="C7" s="65" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="66"/>
+      <c r="E7" s="65" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="67"/>
+      <c r="H7" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="I7" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="J7" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="I7" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="J7" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="K7" s="36" t="s">
-        <v>9</v>
+      <c r="K7" s="35" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="12" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C8" s="13">
         <v>1</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E8" s="14">
         <v>2</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="I8" s="23">
         <v>13</v>
@@ -1811,7 +1862,7 @@
     </row>
     <row r="10" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H10" s="26" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="I10" s="27">
         <v>40</v>
@@ -1825,7 +1876,7 @@
     </row>
     <row r="11" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H11" s="19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="I11" s="20">
         <v>20</v>
@@ -1839,7 +1890,7 @@
     </row>
     <row r="12" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H12" s="19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="I12" s="20">
         <v>10</v>
@@ -1853,7 +1904,7 @@
     </row>
     <row r="13" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H13" s="19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="I13" s="20">
         <v>5</v>
@@ -1867,7 +1918,7 @@
     </row>
     <row r="14" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H14" s="19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="I14" s="20">
         <v>16</v>
@@ -1881,7 +1932,7 @@
     </row>
     <row r="15" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H15" s="19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="I15" s="20">
         <v>8</v>
@@ -1895,7 +1946,7 @@
     </row>
     <row r="16" spans="2:11" x14ac:dyDescent="0.25">
       <c r="H16" s="19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="I16" s="20">
         <v>4</v>
@@ -1909,7 +1960,7 @@
     </row>
     <row r="17" spans="8:11" x14ac:dyDescent="0.25">
       <c r="H17" s="19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="I17" s="20">
         <v>2</v>
@@ -1923,7 +1974,7 @@
     </row>
     <row r="18" spans="8:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H18" s="22" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="I18" s="23">
         <v>1</v>
@@ -1948,12 +1999,12 @@
       <c r="K20" s="1"/>
     </row>
     <row r="21" spans="8:11" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H21" s="71" t="s">
-        <v>12</v>
-      </c>
-      <c r="I21" s="71"/>
-      <c r="J21" s="71"/>
-      <c r="K21" s="71"/>
+      <c r="H21" s="70" t="s">
+        <v>10</v>
+      </c>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
     </row>
     <row r="22" spans="8:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H22" s="1"/>
@@ -1962,30 +2013,30 @@
       <c r="K22" s="1"/>
     </row>
     <row r="23" spans="8:11" x14ac:dyDescent="0.25">
-      <c r="H23" s="34" t="s">
+      <c r="H23" s="33" t="s">
+        <v>6</v>
+      </c>
+      <c r="I23" s="34" t="s">
+        <v>3</v>
+      </c>
+      <c r="J23" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="I23" s="35" t="s">
-        <v>3</v>
-      </c>
-      <c r="J23" s="35" t="s">
-        <v>10</v>
-      </c>
-      <c r="K23" s="36" t="s">
-        <v>9</v>
+      <c r="K23" s="35" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="8:11" ht="60.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H24" s="37" t="s">
-        <v>31</v>
-      </c>
-      <c r="I24" s="38">
+      <c r="H24" s="36" t="s">
+        <v>28</v>
+      </c>
+      <c r="I24" s="37">
         <v>0</v>
       </c>
-      <c r="J24" s="39" t="s">
-        <v>16</v>
-      </c>
-      <c r="K24" s="40">
+      <c r="J24" s="38" t="s">
+        <v>13</v>
+      </c>
+      <c r="K24" s="39">
         <v>2</v>
       </c>
     </row>
@@ -2022,268 +2073,268 @@
   <sheetData>
     <row r="2" spans="2:31" ht="23.25" x14ac:dyDescent="0.35">
       <c r="B2" s="9" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="2:31" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="65" t="s">
-        <v>35</v>
-      </c>
-      <c r="C5" s="65"/>
-      <c r="D5" s="65"/>
-      <c r="E5" s="65"/>
-      <c r="F5" s="65"/>
-      <c r="G5" s="65"/>
-      <c r="H5" s="65"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="65"/>
-      <c r="M5" s="65"/>
-      <c r="N5" s="65"/>
-      <c r="O5" s="65"/>
-      <c r="P5" s="65"/>
-      <c r="Q5" s="65"/>
-      <c r="R5" s="65"/>
-      <c r="S5" s="65"/>
-      <c r="T5" s="65"/>
-      <c r="U5" s="65"/>
-      <c r="V5" s="65"/>
-      <c r="X5" s="65" t="s">
-        <v>17</v>
-      </c>
-      <c r="Y5" s="65"/>
-      <c r="Z5" s="65"/>
+      <c r="B5" s="64" t="s">
+        <v>32</v>
+      </c>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="64"/>
+      <c r="K5" s="64"/>
+      <c r="L5" s="64"/>
+      <c r="M5" s="64"/>
+      <c r="N5" s="64"/>
+      <c r="O5" s="64"/>
+      <c r="P5" s="64"/>
+      <c r="Q5" s="64"/>
+      <c r="R5" s="64"/>
+      <c r="S5" s="64"/>
+      <c r="T5" s="64"/>
+      <c r="U5" s="64"/>
+      <c r="V5" s="64"/>
+      <c r="X5" s="64" t="s">
+        <v>14</v>
+      </c>
+      <c r="Y5" s="64"/>
+      <c r="Z5" s="64"/>
     </row>
     <row r="6" spans="2:31" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="72" t="s">
+      <c r="C7" s="71" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="72"/>
+      <c r="E7" s="72"/>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
+      <c r="J7" s="72"/>
+      <c r="K7" s="72"/>
+      <c r="L7" s="72"/>
+      <c r="M7" s="72"/>
+      <c r="N7" s="72"/>
+      <c r="O7" s="72"/>
+      <c r="P7" s="72"/>
+      <c r="Q7" s="72"/>
+      <c r="R7" s="72"/>
+      <c r="S7" s="72"/>
+      <c r="T7" s="72"/>
+      <c r="U7" s="73"/>
+      <c r="V7" s="44" t="s">
+        <v>17</v>
+      </c>
+      <c r="X7" s="41" t="s">
+        <v>6</v>
+      </c>
+      <c r="Y7" s="63" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z7" s="42" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA7" s="60"/>
+      <c r="AB7" s="60"/>
+      <c r="AC7" s="60"/>
+      <c r="AD7" s="60"/>
+      <c r="AE7" s="60"/>
+    </row>
+    <row r="8" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="B8" s="45">
+        <v>1</v>
+      </c>
+      <c r="C8" s="53">
+        <f t="shared" ref="C8:C17" si="0">IF(MOD(B8,2)=0,B8/2,3*B8+1)</f>
+        <v>4</v>
+      </c>
+      <c r="D8" s="54">
+        <f t="shared" ref="D8:U14" si="1">IF(MOD(C8,2)=0,C8/2,3*C8+1)</f>
+        <v>2</v>
+      </c>
+      <c r="E8" s="54">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F8" s="54">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="G8" s="54">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="H8" s="54">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="I8" s="54">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="J8" s="54">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="K8" s="54">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="L8" s="54">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="M8" s="54">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="N8" s="54">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="O8" s="54">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="P8" s="54">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="Q8" s="54">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="R8" s="54">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="S8" s="54">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="T8" s="54">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="U8" s="55">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="V8" s="45">
+        <v>1</v>
+      </c>
+      <c r="X8" s="61" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y8" s="40">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="62">
+        <f>MATCH(MAX($V$8:V8),$V$8:V8)</f>
+        <v>1</v>
+      </c>
+      <c r="AA8" s="60"/>
+      <c r="AB8" s="60"/>
+      <c r="AC8" s="60"/>
+      <c r="AD8" s="60"/>
+      <c r="AE8" s="60"/>
+    </row>
+    <row r="9" spans="2:31" x14ac:dyDescent="0.25">
+      <c r="B9" s="46">
+        <v>2</v>
+      </c>
+      <c r="C9" s="49">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
+      <c r="D9" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="E9" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F9" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="G9" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="H9" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="I9" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="J9" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K9" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L9" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M9" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="N9" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="O9" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P9" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Q9" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="R9" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S9" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T9" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U9" s="57">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="V9" s="46">
+        <f>MATCH(1,C9:U9,)+1</f>
+        <v>2</v>
+      </c>
+      <c r="X9" s="19" t="s">
         <v>19</v>
-      </c>
-      <c r="D7" s="73"/>
-      <c r="E7" s="73"/>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
-      <c r="J7" s="73"/>
-      <c r="K7" s="73"/>
-      <c r="L7" s="73"/>
-      <c r="M7" s="73"/>
-      <c r="N7" s="73"/>
-      <c r="O7" s="73"/>
-      <c r="P7" s="73"/>
-      <c r="Q7" s="73"/>
-      <c r="R7" s="73"/>
-      <c r="S7" s="73"/>
-      <c r="T7" s="73"/>
-      <c r="U7" s="74"/>
-      <c r="V7" s="45" t="s">
-        <v>20</v>
-      </c>
-      <c r="X7" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="Y7" s="64" t="s">
-        <v>18</v>
-      </c>
-      <c r="Z7" s="43" t="s">
-        <v>10</v>
-      </c>
-      <c r="AA7" s="61"/>
-      <c r="AB7" s="61"/>
-      <c r="AC7" s="61"/>
-      <c r="AD7" s="61"/>
-      <c r="AE7" s="61"/>
-    </row>
-    <row r="8" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B8" s="46">
-        <v>1</v>
-      </c>
-      <c r="C8" s="54">
-        <f t="shared" ref="C8:C17" si="0">IF(MOD(B8,2)=0,B8/2,3*B8+1)</f>
-        <v>4</v>
-      </c>
-      <c r="D8" s="55">
-        <f t="shared" ref="D8:U14" si="1">IF(MOD(C8,2)=0,C8/2,3*C8+1)</f>
-        <v>2</v>
-      </c>
-      <c r="E8" s="55">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="F8" s="55">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="G8" s="55">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="H8" s="55">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="I8" s="55">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="J8" s="55">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="K8" s="55">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="L8" s="55">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="M8" s="55">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="N8" s="55">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="O8" s="55">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="P8" s="55">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="Q8" s="55">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="R8" s="55">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="S8" s="55">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="T8" s="55">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="U8" s="56">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="V8" s="46">
-        <v>1</v>
-      </c>
-      <c r="X8" s="62" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y8" s="41">
-        <v>2</v>
-      </c>
-      <c r="Z8" s="63">
-        <f>MATCH(MAX($V$8:V8),$V$8:V8)</f>
-        <v>1</v>
-      </c>
-      <c r="AA8" s="61"/>
-      <c r="AB8" s="61"/>
-      <c r="AC8" s="61"/>
-      <c r="AD8" s="61"/>
-      <c r="AE8" s="61"/>
-    </row>
-    <row r="9" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B9" s="47">
-        <v>2</v>
-      </c>
-      <c r="C9" s="50">
-        <f t="shared" si="0"/>
-        <v>1</v>
-      </c>
-      <c r="D9" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="E9" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="F9" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="G9" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="H9" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="I9" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="J9" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="K9" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L9" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M9" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="N9" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="O9" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="P9" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="Q9" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="R9" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S9" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="T9" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="U9" s="58">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="V9" s="47">
-        <f>MATCH(1,C9:U9,)+1</f>
-        <v>2</v>
-      </c>
-      <c r="X9" s="19" t="s">
-        <v>22</v>
       </c>
       <c r="Y9" s="20">
         <f>Y8+1</f>
@@ -2293,17 +2344,17 @@
         <f>MATCH(MAX($V$8:V9),$V$8:V9)</f>
         <v>2</v>
       </c>
-      <c r="AA9" s="61"/>
-      <c r="AB9" s="61"/>
-      <c r="AC9" s="61"/>
-      <c r="AD9" s="61"/>
-      <c r="AE9" s="61"/>
+      <c r="AA9" s="60"/>
+      <c r="AB9" s="60"/>
+      <c r="AC9" s="60"/>
+      <c r="AD9" s="60"/>
+      <c r="AE9" s="60"/>
     </row>
     <row r="10" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B10" s="47">
+      <c r="B10" s="46">
         <v>3</v>
       </c>
-      <c r="C10" s="44">
+      <c r="C10" s="43">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -2327,64 +2378,64 @@
         <f t="shared" si="4"/>
         <v>2</v>
       </c>
-      <c r="I10" s="51">
+      <c r="I10" s="50">
         <f t="shared" ref="I10" si="5">IF(MOD(H10,2)=0,H10/2,3*H10+1)</f>
         <v>1</v>
       </c>
-      <c r="J10" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="K10" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="L10" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="M10" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="N10" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="O10" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="P10" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="Q10" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="R10" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="S10" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="T10" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="U10" s="58">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="V10" s="47">
+      <c r="J10" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="K10" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="L10" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="M10" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="N10" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="O10" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="P10" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="Q10" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="R10" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="S10" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T10" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U10" s="57">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="V10" s="46">
         <f t="shared" ref="V10:V17" si="6">MATCH(1,C10:U10,)+1</f>
         <v>8</v>
       </c>
       <c r="X10" s="19" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="Y10" s="20">
         <f t="shared" ref="Y10:Y17" si="7">Y9+1</f>
@@ -2394,98 +2445,98 @@
         <f>MATCH(MAX($V$8:V10),$V$8:V10)</f>
         <v>3</v>
       </c>
-      <c r="AA10" s="61"/>
-      <c r="AB10" s="61"/>
-      <c r="AC10" s="61"/>
-      <c r="AD10" s="61"/>
-      <c r="AE10" s="61"/>
+      <c r="AA10" s="60"/>
+      <c r="AB10" s="60"/>
+      <c r="AC10" s="60"/>
+      <c r="AD10" s="60"/>
+      <c r="AE10" s="60"/>
     </row>
     <row r="11" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B11" s="47">
-        <v>4</v>
-      </c>
-      <c r="C11" s="44">
+      <c r="B11" s="46">
+        <v>4</v>
+      </c>
+      <c r="C11" s="43">
         <f t="shared" si="0"/>
         <v>2</v>
       </c>
-      <c r="D11" s="51">
+      <c r="D11" s="50">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="E11" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="F11" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="G11" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="H11" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="I11" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="J11" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K11" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L11" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="M11" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N11" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="O11" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="P11" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q11" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="R11" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="S11" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="T11" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="U11" s="58">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="V11" s="47">
+      <c r="E11" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="F11" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="G11" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="H11" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="I11" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J11" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K11" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L11" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="M11" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N11" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="O11" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P11" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q11" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="R11" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S11" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T11" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="U11" s="57">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="V11" s="46">
         <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="X11" s="19" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="Y11" s="20">
         <f t="shared" si="7"/>
@@ -2495,17 +2546,17 @@
         <f>MATCH(MAX($V$8:V11),$V$8:V11)</f>
         <v>3</v>
       </c>
-      <c r="AA11" s="61"/>
-      <c r="AB11" s="61"/>
-      <c r="AC11" s="61"/>
-      <c r="AD11" s="61"/>
-      <c r="AE11" s="61"/>
+      <c r="AA11" s="60"/>
+      <c r="AB11" s="60"/>
+      <c r="AC11" s="60"/>
+      <c r="AD11" s="60"/>
+      <c r="AE11" s="60"/>
     </row>
     <row r="12" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B12" s="47">
+      <c r="B12" s="46">
         <v>5</v>
       </c>
-      <c r="C12" s="44">
+      <c r="C12" s="43">
         <f t="shared" si="0"/>
         <v>16</v>
       </c>
@@ -2521,72 +2572,72 @@
         <f t="shared" si="8"/>
         <v>2</v>
       </c>
-      <c r="G12" s="51">
+      <c r="G12" s="50">
         <f t="shared" ref="G12" si="9">IF(MOD(F12,2)=0,F12/2,3*F12+1)</f>
         <v>1</v>
       </c>
-      <c r="H12" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="I12" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="J12" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="K12" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L12" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="M12" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N12" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="O12" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="P12" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q12" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="R12" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="S12" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="T12" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="U12" s="58">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="V12" s="47">
+      <c r="H12" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="I12" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="J12" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="K12" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L12" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="M12" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N12" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="O12" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P12" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q12" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="R12" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S12" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T12" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="U12" s="57">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="V12" s="46">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
       <c r="X12" s="19" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Y12" s="20">
         <f t="shared" si="7"/>
@@ -2596,17 +2647,17 @@
         <f>MATCH(MAX($V$8:V12),$V$8:V12)</f>
         <v>3</v>
       </c>
-      <c r="AA12" s="61"/>
-      <c r="AB12" s="61"/>
-      <c r="AC12" s="61"/>
-      <c r="AD12" s="61"/>
-      <c r="AE12" s="61"/>
+      <c r="AA12" s="60"/>
+      <c r="AB12" s="60"/>
+      <c r="AC12" s="60"/>
+      <c r="AD12" s="60"/>
+      <c r="AE12" s="60"/>
     </row>
     <row r="13" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B13" s="47">
+      <c r="B13" s="46">
         <v>6</v>
       </c>
-      <c r="C13" s="44">
+      <c r="C13" s="43">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
@@ -2634,60 +2685,60 @@
         <f t="shared" ref="I13:J13" si="12">IF(MOD(H13,2)=0,H13/2,3*H13+1)</f>
         <v>2</v>
       </c>
-      <c r="J13" s="51">
+      <c r="J13" s="50">
         <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="K13" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L13" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="M13" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="N13" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="O13" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="P13" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="Q13" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="R13" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="S13" s="57">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="T13" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="U13" s="58">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="V13" s="47">
+      <c r="K13" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="L13" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="M13" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="N13" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="O13" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="P13" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="Q13" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="R13" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="S13" s="56">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="T13" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="U13" s="57">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="V13" s="46">
         <f t="shared" si="6"/>
         <v>9</v>
       </c>
       <c r="X13" s="19" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Y13" s="20">
         <f t="shared" si="7"/>
@@ -2697,17 +2748,17 @@
         <f>MATCH(MAX($V$8:V13),$V$8:V13)</f>
         <v>6</v>
       </c>
-      <c r="AA13" s="61"/>
-      <c r="AB13" s="61"/>
-      <c r="AC13" s="61"/>
-      <c r="AD13" s="61"/>
-      <c r="AE13" s="61"/>
+      <c r="AA13" s="60"/>
+      <c r="AB13" s="60"/>
+      <c r="AC13" s="60"/>
+      <c r="AD13" s="60"/>
+      <c r="AE13" s="60"/>
     </row>
     <row r="14" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B14" s="47">
+      <c r="B14" s="46">
         <v>7</v>
       </c>
-      <c r="C14" s="44">
+      <c r="C14" s="43">
         <f t="shared" si="0"/>
         <v>22</v>
       </c>
@@ -2767,28 +2818,28 @@
         <f t="shared" si="16"/>
         <v>2</v>
       </c>
-      <c r="R14" s="51">
+      <c r="R14" s="50">
         <f t="shared" si="16"/>
         <v>1</v>
       </c>
-      <c r="S14" s="57">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="T14" s="57">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="U14" s="58">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="V14" s="47">
+      <c r="S14" s="56">
+        <f t="shared" si="1"/>
+        <v>4</v>
+      </c>
+      <c r="T14" s="56">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="U14" s="57">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="V14" s="46">
         <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="X14" s="19" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="Y14" s="20">
         <f t="shared" si="7"/>
@@ -2798,17 +2849,17 @@
         <f>MATCH(MAX($V$8:V14),$V$8:V14)</f>
         <v>7</v>
       </c>
-      <c r="AA14" s="61"/>
-      <c r="AB14" s="61"/>
-      <c r="AC14" s="61"/>
-      <c r="AD14" s="61"/>
-      <c r="AE14" s="61"/>
+      <c r="AA14" s="60"/>
+      <c r="AB14" s="60"/>
+      <c r="AC14" s="60"/>
+      <c r="AD14" s="60"/>
+      <c r="AE14" s="60"/>
     </row>
     <row r="15" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B15" s="47">
+      <c r="B15" s="46">
         <v>8</v>
       </c>
-      <c r="C15" s="44">
+      <c r="C15" s="43">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
@@ -2816,80 +2867,80 @@
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
-      <c r="E15" s="51">
+      <c r="E15" s="50">
         <f t="shared" ref="E15" si="17">IF(MOD(D15,2)=0,D15/2,3*D15+1)</f>
         <v>1</v>
       </c>
-      <c r="F15" s="57">
+      <c r="F15" s="56">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="G15" s="57">
+      <c r="G15" s="56">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="H15" s="57">
+      <c r="H15" s="56">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="I15" s="57">
+      <c r="I15" s="56">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="J15" s="57">
+      <c r="J15" s="56">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="K15" s="57">
+      <c r="K15" s="56">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="L15" s="57">
+      <c r="L15" s="56">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="M15" s="57">
+      <c r="M15" s="56">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="N15" s="57">
+      <c r="N15" s="56">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="O15" s="57">
+      <c r="O15" s="56">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="P15" s="57">
+      <c r="P15" s="56">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="Q15" s="57">
+      <c r="Q15" s="56">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="R15" s="57">
+      <c r="R15" s="56">
         <f t="shared" si="13"/>
         <v>4</v>
       </c>
-      <c r="S15" s="57">
+      <c r="S15" s="56">
         <f t="shared" si="13"/>
         <v>2</v>
       </c>
-      <c r="T15" s="57">
+      <c r="T15" s="56">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="U15" s="58">
+      <c r="U15" s="57">
         <f t="shared" ref="U15" si="18">IF(MOD(T15,2)=0,T15/2,3*T15+1)</f>
         <v>4</v>
       </c>
-      <c r="V15" s="47">
+      <c r="V15" s="46">
         <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="X15" s="19" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="Y15" s="20">
         <f t="shared" si="7"/>
@@ -2899,17 +2950,17 @@
         <f>MATCH(MAX($V$8:V15),$V$8:V15)</f>
         <v>7</v>
       </c>
-      <c r="AA15" s="61"/>
-      <c r="AB15" s="61"/>
-      <c r="AC15" s="61"/>
-      <c r="AD15" s="61"/>
-      <c r="AE15" s="61"/>
+      <c r="AA15" s="60"/>
+      <c r="AB15" s="60"/>
+      <c r="AC15" s="60"/>
+      <c r="AD15" s="60"/>
+      <c r="AE15" s="60"/>
     </row>
     <row r="16" spans="2:31" x14ac:dyDescent="0.25">
-      <c r="B16" s="47">
+      <c r="B16" s="46">
         <v>9</v>
       </c>
-      <c r="C16" s="44">
+      <c r="C16" s="43">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
@@ -2981,16 +3032,16 @@
         <f t="shared" si="23"/>
         <v>2</v>
       </c>
-      <c r="U16" s="52">
+      <c r="U16" s="51">
         <f t="shared" si="23"/>
         <v>1</v>
       </c>
-      <c r="V16" s="47">
+      <c r="V16" s="46">
         <f t="shared" si="6"/>
         <v>20</v>
       </c>
       <c r="X16" s="19" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="Y16" s="20">
         <f t="shared" si="7"/>
@@ -3000,17 +3051,17 @@
         <f>MATCH(MAX($V$8:V16),$V$8:V16)</f>
         <v>9</v>
       </c>
-      <c r="AA16" s="61"/>
-      <c r="AB16" s="61"/>
-      <c r="AC16" s="61"/>
-      <c r="AD16" s="61"/>
-      <c r="AE16" s="61"/>
+      <c r="AA16" s="60"/>
+      <c r="AB16" s="60"/>
+      <c r="AC16" s="60"/>
+      <c r="AD16" s="60"/>
+      <c r="AE16" s="60"/>
     </row>
     <row r="17" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="48">
+      <c r="B17" s="47">
         <v>10</v>
       </c>
-      <c r="C17" s="49">
+      <c r="C17" s="48">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
@@ -3030,68 +3081,68 @@
         <f t="shared" ref="G17:H17" si="25">IF(MOD(F17,2)=0,F17/2,3*F17+1)</f>
         <v>2</v>
       </c>
-      <c r="H17" s="53">
+      <c r="H17" s="52">
         <f t="shared" si="25"/>
         <v>1</v>
       </c>
-      <c r="I17" s="59">
+      <c r="I17" s="58">
         <f t="shared" si="21"/>
         <v>4</v>
       </c>
-      <c r="J17" s="59">
+      <c r="J17" s="58">
         <f t="shared" si="21"/>
         <v>2</v>
       </c>
-      <c r="K17" s="59">
+      <c r="K17" s="58">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
-      <c r="L17" s="59">
+      <c r="L17" s="58">
         <f t="shared" si="21"/>
         <v>4</v>
       </c>
-      <c r="M17" s="59">
+      <c r="M17" s="58">
         <f t="shared" si="21"/>
         <v>2</v>
       </c>
-      <c r="N17" s="59">
+      <c r="N17" s="58">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
-      <c r="O17" s="59">
+      <c r="O17" s="58">
         <f t="shared" si="21"/>
         <v>4</v>
       </c>
-      <c r="P17" s="59">
+      <c r="P17" s="58">
         <f t="shared" si="21"/>
         <v>2</v>
       </c>
-      <c r="Q17" s="59">
+      <c r="Q17" s="58">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
-      <c r="R17" s="59">
+      <c r="R17" s="58">
         <f t="shared" si="21"/>
         <v>4</v>
       </c>
-      <c r="S17" s="59">
+      <c r="S17" s="58">
         <f t="shared" si="21"/>
         <v>2</v>
       </c>
-      <c r="T17" s="59">
+      <c r="T17" s="58">
         <f t="shared" si="21"/>
         <v>1</v>
       </c>
-      <c r="U17" s="60">
+      <c r="U17" s="59">
         <f t="shared" si="21"/>
         <v>4</v>
       </c>
-      <c r="V17" s="48">
+      <c r="V17" s="47">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="X17" s="22" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="Y17" s="23">
         <f t="shared" si="7"/>
@@ -3101,11 +3152,11 @@
         <f>MATCH(MAX($V$8:V17),$V$8:V17)</f>
         <v>9</v>
       </c>
-      <c r="AA17" s="61"/>
-      <c r="AB17" s="61"/>
-      <c r="AC17" s="61"/>
-      <c r="AD17" s="61"/>
-      <c r="AE17" s="61"/>
+      <c r="AA17" s="60"/>
+      <c r="AB17" s="60"/>
+      <c r="AC17" s="60"/>
+      <c r="AD17" s="60"/>
+      <c r="AE17" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="3">

--- a/src/test/res/disegno-pruebas-secuencias-collatz.xlsx
+++ b/src/test/res/disegno-pruebas-secuencias-collatz.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11115" windowHeight="7935"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="11115" windowHeight="7935" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Diseño pruebas siguienteCollatz" sheetId="2" r:id="rId1"/>
@@ -968,44 +968,44 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="33" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="38" xfId="4" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="41" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="42" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="40" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="2" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="33" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="31" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="38" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -1032,16 +1032,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>144780</xdr:colOff>
-      <xdr:row>5</xdr:row>
-      <xdr:rowOff>38100</xdr:rowOff>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>297180</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>144780</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>419100</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>344805</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1050,13 +1050,13 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="7848600" y="518160"/>
-          <a:ext cx="1973580" cy="1592580"/>
+          <a:off x="1278255" y="3114675"/>
+          <a:ext cx="1912620" cy="1668780"/>
         </a:xfrm>
         <a:prstGeom prst="wedgeRoundRectCallout">
           <a:avLst>
-            <a:gd name="adj1" fmla="val -95737"/>
-            <a:gd name="adj2" fmla="val 42968"/>
+            <a:gd name="adj1" fmla="val 100478"/>
+            <a:gd name="adj2" fmla="val -70046"/>
             <a:gd name="adj3" fmla="val 16667"/>
           </a:avLst>
         </a:prstGeom>
@@ -1494,33 +1494,33 @@
       </c>
     </row>
     <row r="5" spans="2:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="I5" s="64" t="s">
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="I5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
     </row>
     <row r="6" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="66"/>
-      <c r="E7" s="65" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="67"/>
+      <c r="C7" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="70"/>
+      <c r="E7" s="69" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="71"/>
       <c r="I7" s="16" t="s">
         <v>6</v>
       </c>
@@ -1535,7 +1535,7 @@
       </c>
     </row>
     <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="72" t="s">
         <v>3</v>
       </c>
       <c r="C8" s="2">
@@ -1564,15 +1564,15 @@
       </c>
     </row>
     <row r="9" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="74"/>
-      <c r="C9" s="75">
-        <v>2</v>
-      </c>
-      <c r="D9" s="76" t="s">
+      <c r="B9" s="73"/>
+      <c r="C9" s="64">
+        <v>2</v>
+      </c>
+      <c r="D9" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="E9" s="75"/>
-      <c r="F9" s="77"/>
+      <c r="E9" s="64"/>
+      <c r="F9" s="66"/>
       <c r="I9" s="22" t="s">
         <v>19</v>
       </c>
@@ -1587,7 +1587,7 @@
       </c>
     </row>
     <row r="10" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="69"/>
+      <c r="B10" s="74"/>
       <c r="C10" s="6">
         <v>3</v>
       </c>
@@ -1706,12 +1706,12 @@
       </c>
     </row>
     <row r="20" spans="9:12" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="I20" s="64" t="s">
+      <c r="I20" s="68" t="s">
         <v>10</v>
       </c>
-      <c r="J20" s="64"/>
-      <c r="K20" s="64"/>
-      <c r="L20" s="64"/>
+      <c r="J20" s="68"/>
+      <c r="K20" s="68"/>
+      <c r="L20" s="68"/>
     </row>
     <row r="21" spans="9:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="22" spans="9:12" x14ac:dyDescent="0.25">
@@ -1735,7 +1735,7 @@
       <c r="J23" s="31">
         <v>0</v>
       </c>
-      <c r="K23" s="78" t="s">
+      <c r="K23" s="67" t="s">
         <v>37</v>
       </c>
       <c r="L23" s="32">
@@ -1780,33 +1780,33 @@
       </c>
     </row>
     <row r="5" spans="2:11" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="68" t="s">
         <v>5</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="H5" s="64" t="s">
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="H5" s="68" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
     </row>
     <row r="6" spans="2:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="C7" s="65" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" s="66"/>
-      <c r="E7" s="65" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="67"/>
+      <c r="C7" s="69" t="s">
+        <v>1</v>
+      </c>
+      <c r="D7" s="70"/>
+      <c r="E7" s="69" t="s">
+        <v>2</v>
+      </c>
+      <c r="F7" s="71"/>
       <c r="H7" s="33" t="s">
         <v>6</v>
       </c>
@@ -1999,12 +1999,12 @@
       <c r="K20" s="1"/>
     </row>
     <row r="21" spans="8:11" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="H21" s="70" t="s">
+      <c r="H21" s="75" t="s">
         <v>10</v>
       </c>
-      <c r="I21" s="70"/>
-      <c r="J21" s="70"/>
-      <c r="K21" s="70"/>
+      <c r="I21" s="75"/>
+      <c r="J21" s="75"/>
+      <c r="K21" s="75"/>
     </row>
     <row r="22" spans="8:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="H22" s="1"/>
@@ -2077,61 +2077,61 @@
       </c>
     </row>
     <row r="5" spans="2:31" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B5" s="64" t="s">
+      <c r="B5" s="68" t="s">
         <v>32</v>
       </c>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="64"/>
-      <c r="K5" s="64"/>
-      <c r="L5" s="64"/>
-      <c r="M5" s="64"/>
-      <c r="N5" s="64"/>
-      <c r="O5" s="64"/>
-      <c r="P5" s="64"/>
-      <c r="Q5" s="64"/>
-      <c r="R5" s="64"/>
-      <c r="S5" s="64"/>
-      <c r="T5" s="64"/>
-      <c r="U5" s="64"/>
-      <c r="V5" s="64"/>
-      <c r="X5" s="64" t="s">
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
+      <c r="L5" s="68"/>
+      <c r="M5" s="68"/>
+      <c r="N5" s="68"/>
+      <c r="O5" s="68"/>
+      <c r="P5" s="68"/>
+      <c r="Q5" s="68"/>
+      <c r="R5" s="68"/>
+      <c r="S5" s="68"/>
+      <c r="T5" s="68"/>
+      <c r="U5" s="68"/>
+      <c r="V5" s="68"/>
+      <c r="X5" s="68" t="s">
         <v>14</v>
       </c>
-      <c r="Y5" s="64"/>
-      <c r="Z5" s="64"/>
+      <c r="Y5" s="68"/>
+      <c r="Z5" s="68"/>
     </row>
     <row r="6" spans="2:31" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="7" spans="2:31" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C7" s="71" t="s">
+      <c r="C7" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="72"/>
-      <c r="E7" s="72"/>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-      <c r="J7" s="72"/>
-      <c r="K7" s="72"/>
-      <c r="L7" s="72"/>
-      <c r="M7" s="72"/>
-      <c r="N7" s="72"/>
-      <c r="O7" s="72"/>
-      <c r="P7" s="72"/>
-      <c r="Q7" s="72"/>
-      <c r="R7" s="72"/>
-      <c r="S7" s="72"/>
-      <c r="T7" s="72"/>
-      <c r="U7" s="73"/>
+      <c r="D7" s="77"/>
+      <c r="E7" s="77"/>
+      <c r="F7" s="77"/>
+      <c r="G7" s="77"/>
+      <c r="H7" s="77"/>
+      <c r="I7" s="77"/>
+      <c r="J7" s="77"/>
+      <c r="K7" s="77"/>
+      <c r="L7" s="77"/>
+      <c r="M7" s="77"/>
+      <c r="N7" s="77"/>
+      <c r="O7" s="77"/>
+      <c r="P7" s="77"/>
+      <c r="Q7" s="77"/>
+      <c r="R7" s="77"/>
+      <c r="S7" s="77"/>
+      <c r="T7" s="77"/>
+      <c r="U7" s="78"/>
       <c r="V7" s="44" t="s">
         <v>17</v>
       </c>
